--- a/resampling/input/accessibility_reports_generated/Save the Children_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/Save the Children_accessibility_report.xlsx
@@ -184,8 +184,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q55" headerRowCount="1">
-  <autoFilter ref="A1:Q55"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q96" headerRowCount="1">
+  <autoFilter ref="A1:Q96"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -210,8 +210,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O79" headerRowCount="1">
-  <autoFilter ref="A1:O79"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O76" headerRowCount="1">
+  <autoFilter ref="A1:O76"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -553,7 +553,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 54 wards, 78 clusters</t>
+          <t>Assigned to you: 95 wards, 75 clusters</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -833,7 +833,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yaav</t>
+          <t>Liev L</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -845,13 +845,13 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mbaikyor</t>
+          <t>Liev Ll</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -892,7 +892,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kumakwagh</t>
+          <t>Mbaikyor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -927,13 +927,13 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>2</v>
-      </c>
       <c r="J4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -956,7 +956,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Liev Ll</t>
+          <t>Menev</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -968,13 +968,13 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1009,13 +1009,13 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Liev L</t>
+          <t>Yaav</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1050,13 +1050,13 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mbaketsa</t>
+          <t>Mbadura</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1091,13 +1091,13 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Agba / Kyan</t>
+          <t>Mbaketsa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1138,7 +1138,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Township</t>
+          <t>Agba / Kyan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Menev</t>
+          <t>Mbakyaha</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1214,13 +1214,13 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Bebi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1255,13 +1255,13 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tondov L</t>
+          <t>Becheve</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1296,13 +1296,13 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mbadura</t>
+          <t>Bete</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1337,13 +1337,13 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mbakyaha</t>
+          <t>Bishiri North</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1378,13 +1378,13 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Usar</t>
+          <t>Kashimbila</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1419,13 +1419,13 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mbayoo</t>
+          <t>Kumakwagh</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1460,7 +1460,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1479,17 +1479,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mai'adua A</t>
+          <t>Mbagbera</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1520,17 +1520,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Danyashe</t>
+          <t>Mbatyough</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1542,13 +1542,13 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1561,17 +1561,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Natsalle</t>
+          <t>Mbayoo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1583,13 +1583,13 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1602,43 +1602,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ubandawaki A</t>
+          <t>Michihe</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Daura</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1651,17 +1643,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Maikoni A</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1673,13 +1665,13 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1692,17 +1684,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bumbum B</t>
+          <t>Tondov L</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1714,13 +1706,13 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1733,17 +1725,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Maikoni B</t>
+          <t>Township</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1755,13 +1747,13 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1774,43 +1766,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gallu</t>
+          <t>Usar</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Mashi</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1823,17 +1807,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Koza</t>
+          <t>Utanga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1845,13 +1829,13 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1864,17 +1848,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mai'adua C</t>
+          <t>Utange</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1886,13 +1870,13 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1915,33 +1899,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sabon Gari</t>
+          <t>Mai'adua A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Daura; Funtua; Rimi</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>1</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -1964,7 +1940,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bamle</t>
+          <t>Ubandawaki A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1975,7 +1951,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mashi</t>
+          <t>Daura</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1984,13 +1960,13 @@
         </is>
       </c>
       <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
         <v>1</v>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2013,25 +1989,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bumbum A</t>
+          <t>Danyashe</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dutsi; Mashi</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2054,7 +2038,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ubandawaki B</t>
+          <t>Maikoni A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2074,13 +2058,13 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2098,30 +2082,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Garni</t>
+          <t>Natsalle</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2139,30 +2131,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rogogo</t>
+          <t>Gallu</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kanda</t>
+          <t>Maikoni B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2197,13 +2197,13 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2221,12 +2221,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Bumbum B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -2244,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2262,38 +2262,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>K Malamai</t>
+          <t>Koza</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Baure</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
         <v>2</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>9</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2311,30 +2303,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dargage</t>
+          <t>Sabon Gari</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bindawa; Charanchi; Daura; Funtua; Mani; Rimi; Sandamu</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
         <v>2</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>7</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2352,22 +2352,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kawarin Kudi</t>
+          <t>Bamle</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>1</v>
       </c>
@@ -2375,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -2393,30 +2401,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fago B</t>
+          <t>Bumbum A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Sandamu</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>1</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -2442,22 +2442,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gwamba</t>
+          <t>Ubandawaki B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Daura</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>1</v>
       </c>
@@ -2465,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2483,12 +2491,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Maibara</t>
+          <t>Karkarku</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2499,7 +2507,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Baure</t>
+          <t>Daura; Sandamu</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2508,7 +2516,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -2527,17 +2535,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kotorkoshi</t>
+          <t>Kusugu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2548,7 +2556,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tsafe</t>
+          <t>Daura</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2557,13 +2565,13 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -2576,17 +2584,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bela Rawaiya</t>
+          <t>Kwasarawa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2597,7 +2605,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gusau; Kaura Namoda</t>
+          <t>Sandamu; Zango</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2606,13 +2614,13 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2625,43 +2633,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gada Karakai</t>
+          <t>Mai'adua B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Maradun</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2674,43 +2674,35 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Furfuri Kwaikwai</t>
+          <t>Mai'adua C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Gusau</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -2723,35 +2715,43 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Samawa</t>
+          <t>Mazoji A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Daura; Matazu</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -2764,35 +2764,43 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bingi South</t>
+          <t>Mazoji B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Daura; Matazu</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -2805,35 +2813,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Sirika B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Daura; Dutsi; Mani</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -2846,35 +2862,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nahuche</t>
+          <t>Sonkaya</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dutsi; Mashi</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -2887,35 +2911,43 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sankalawa</t>
+          <t>Garni</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Baure; Sandamu</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -2928,43 +2960,35 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ruwan Doruma</t>
+          <t>Rogogo</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Maru</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -2977,17 +3001,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tofa</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2999,13 +3023,13 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3018,17 +3042,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>K Malamai</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -3039,7 +3063,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Baure</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3048,13 +3072,13 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3067,17 +3091,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mayana</t>
+          <t>Dargage</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -3088,7 +3112,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gusau</t>
+          <t>Sandamu</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3097,13 +3121,13 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3116,43 +3140,35 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tudun Wada</t>
+          <t>Kanda</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Gusau</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3162,23 +3178,2000 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Kawarin Kudi</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Baure</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>6</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" s="10" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Fago B</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" s="10" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Gwamba</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" s="10" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Baure</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Baure; Bindawa; Mani</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" s="10" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Faski</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Baure</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" s="10" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Gwarta</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Baure</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" s="10" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Kagare</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" s="10" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Katsayal</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" s="10" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Kwasarawa</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mai'adua; Sandamu</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" s="10" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Maibara</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Baure</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" s="10" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Yanduna</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Baure</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" s="10" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Yardaje</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" s="10" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Furfuri Kwaikwai</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>7</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>24</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" s="10" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Bela Rawaiya</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Gusau; Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>4</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2</v>
+      </c>
+      <c r="J69" t="n">
+        <v>19</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" s="10" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Kotorkoshi</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Gusau; Tsafe</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>14</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" s="10" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Nahuche</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>2</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>8</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" s="10" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Bingi North</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Gusau; Maru</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>6</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" s="10" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" t="n">
+        <v>5</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" s="10" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Sankalawa</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>5</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" s="10" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Maradun; Maru</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" s="10" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Bindin</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Anka; Maru</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" s="10" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Bingi</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" s="10" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Bingi South</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gusau; Maru</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" s="10" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Damaga Gamagiwa</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Maradun; Maru</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" s="10" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Dan' Isa</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" s="10" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Gada Karakai</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Maradun; Maru</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" s="10" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Galadima</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Anka; Bakura; Gusau; Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" s="10" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Kagara</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Kaura Namoda; Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" s="10" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Kanoma</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Anka; Maru; Talata Mafara</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" s="10" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Kurya</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Kaura Namoda; Maradun; Shinkafi; Zurmi</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" s="10" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Kyambarawa</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Kaura Namoda</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" s="10" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Magami</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Gusau; Maru; Tsafe</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" s="10" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Mayana</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" s="10" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Rijiya</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Gusau; Tsafe</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" s="10" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ruwan Doruma</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Maru</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" s="10" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Samawa</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" s="10" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Tofa</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Gusau</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" s="10" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Tudun Wada</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" s="10" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Wanke</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Gusau; Tsafe</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" s="10" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Wonaka</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Gusau; Tsafe</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" s="10" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Yandoton Daji</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Gusau; Tsafe</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" s="10" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="K2:K55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O55" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="O2:O96" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3194,7 +5187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3402,7 +5395,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kumakwagh</t>
+          <t>Liev Ll</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3412,7 +5405,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>idp_NG007011_17</t>
+          <t>idp_NG007011_3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3451,7 +5444,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Liev Ll</t>
+          <t>Mbaikyor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3461,7 +5454,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>idp_NG007011_3</t>
+          <t>idp_NG007011_5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3471,12 +5464,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -3500,7 +5493,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kumakwagh</t>
+          <t>Yaav</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3510,7 +5503,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>idp_NG007011_4</t>
+          <t>idp_NG007011_8</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3520,12 +5513,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -3549,7 +5542,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mbaikyor</t>
+          <t>Mbadura</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3559,7 +5552,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>idp_NG007011_5</t>
+          <t>idp_NG007011_supp1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3569,12 +5562,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -3598,32 +5591,28 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yaav</t>
+          <t>Mbaikyor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>idp_NG007011_8</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_10</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -3647,7 +5636,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tondov L</t>
+          <t>Menev</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3657,7 +5646,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_1</t>
+          <t>non_idp_NG007011_11</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3692,7 +5681,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mbaikyor</t>
+          <t>Menev</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3702,7 +5691,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_10</t>
+          <t>non_idp_NG007011_12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -3737,7 +5726,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Menev</t>
+          <t>Liev Ll</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3747,7 +5736,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_11</t>
+          <t>non_idp_NG007011_13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -3782,7 +5771,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Menev</t>
+          <t>Mbaketsa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3792,7 +5781,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_12</t>
+          <t>non_idp_NG007011_14</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -3827,7 +5816,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liev Ll</t>
+          <t>Yaav</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3837,7 +5826,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_13</t>
+          <t>non_idp_NG007011_16</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -3872,7 +5861,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mbaketsa</t>
+          <t>Mbaikyor</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3882,7 +5871,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_14</t>
+          <t>non_idp_NG007011_17</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -3917,7 +5906,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kumakwagh</t>
+          <t>Mbaketsa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3927,7 +5916,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_15</t>
+          <t>non_idp_NG007011_2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -3962,7 +5951,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yaav</t>
+          <t>Usar</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3972,7 +5961,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_16</t>
+          <t>non_idp_NG007011_3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -4007,7 +5996,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Liev L</t>
+          <t>Mbaikyor</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4017,7 +6006,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_17</t>
+          <t>non_idp_NG007011_4</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -4052,7 +6041,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mbaketsa</t>
+          <t>Tondov Ll</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4062,7 +6051,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_2</t>
+          <t>non_idp_NG007011_5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -4097,7 +6086,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Township</t>
+          <t>Agba / Kyan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4107,7 +6096,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_3</t>
+          <t>non_idp_NG007011_7</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -4142,7 +6131,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mbaikyor</t>
+          <t>Tondov Ll</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4152,7 +6141,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_4</t>
+          <t>non_idp_NG007011_8</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -4187,7 +6176,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tondov Ll</t>
+          <t>Agba / Kyan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4197,7 +6186,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_5</t>
+          <t>non_idp_NG007011_9</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4232,7 +6221,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Liev L</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4242,7 +6231,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_6</t>
+          <t>non_idp_NG007011_supp1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -4277,7 +6266,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Township</t>
+          <t>Liev Ll</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4287,7 +6276,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_7</t>
+          <t>non_idp_NG007011_supp2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -4312,38 +6301,42 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Benue</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kwande</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tondov Ll</t>
+          <t>Mai'adua A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_8</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>idp_NG021024_1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -4357,30 +6350,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Benue</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kwande</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Agba / Kyan</t>
+          <t>Ubandawaki A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_9</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>idp_NG021024_10</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>6</t>
@@ -4412,32 +6409,28 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mai'adua A</t>
+          <t>Gallu</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>idp_NG021024_1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -4461,24 +6454,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ubandawaki A</t>
+          <t>Danyashe</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>idp_NG021024_10</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_10</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>6</t>
@@ -4510,7 +6499,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gallu</t>
+          <t>Natsalle</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4520,7 +6509,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_1</t>
+          <t>non_idp_NG021024_11</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -4555,7 +6544,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Danyashe</t>
+          <t>Maikoni B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4565,7 +6554,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_10</t>
+          <t>non_idp_NG021024_12</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -4600,7 +6589,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Natsalle</t>
+          <t>Maikoni A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4610,18 +6599,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_11</t>
+          <t>non_idp_NG021024_13</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4645,7 +6634,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Koza</t>
+          <t>Ubandawaki A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4655,18 +6644,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_12</t>
+          <t>non_idp_NG021024_15</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4690,7 +6679,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Maikoni A</t>
+          <t>Bumbum B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4700,18 +6689,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_13</t>
+          <t>non_idp_NG021024_17</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4735,7 +6724,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ubandawaki A</t>
+          <t>Natsalle</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4745,18 +6734,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_15</t>
+          <t>non_idp_NG021024_2</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4780,7 +6769,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bumbum B</t>
+          <t>Natsalle</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4790,7 +6779,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_17</t>
+          <t>non_idp_NG021024_3</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -4825,7 +6814,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Natsalle</t>
+          <t>Danyashe</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4835,7 +6824,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_2</t>
+          <t>non_idp_NG021024_4</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -4870,7 +6859,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bumbum B</t>
+          <t>Natsalle</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4880,7 +6869,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_3</t>
+          <t>non_idp_NG021024_5</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -4925,7 +6914,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_4</t>
+          <t>non_idp_NG021024_6</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -4970,7 +6959,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_5</t>
+          <t>non_idp_NG021024_7</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -5005,7 +6994,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Danyashe</t>
+          <t>Maikoni A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5015,7 +7004,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_6</t>
+          <t>non_idp_NG021024_8</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -5050,7 +7039,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Natsalle</t>
+          <t>Maikoni A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5060,7 +7049,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_7</t>
+          <t>non_idp_NG021024_9</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -5090,12 +7079,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Maikoni A</t>
+          <t>Dargage</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5105,7 +7094,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_8</t>
+          <t>non_idp_NG021034_1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -5135,12 +7124,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Maikoni A</t>
+          <t>K Malamai</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5150,7 +7139,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_9</t>
+          <t>non_idp_NG021034_11</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -5185,7 +7174,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dargage</t>
+          <t>Kanda</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5195,7 +7184,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_1</t>
+          <t>non_idp_NG021034_12</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -5230,7 +7219,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rogogo</t>
+          <t>Gwamba</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5240,18 +7229,18 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_11</t>
+          <t>non_idp_NG021034_13</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5275,7 +7264,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kanda</t>
+          <t>K Malamai</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5285,7 +7274,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_12</t>
+          <t>non_idp_NG021034_15</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -5320,7 +7309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kanda</t>
+          <t>Kawarin Kudi</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5330,18 +7319,18 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_13</t>
+          <t>non_idp_NG021034_16</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5365,7 +7354,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>K Malamai</t>
+          <t>Garni</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5375,7 +7364,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_15</t>
+          <t>non_idp_NG021034_17</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -5410,7 +7399,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kawarin Kudi</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5420,7 +7409,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_16</t>
+          <t>non_idp_NG021034_2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -5465,7 +7454,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_17</t>
+          <t>non_idp_NG021034_3</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -5500,7 +7489,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Rogogo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5510,7 +7499,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_2</t>
+          <t>non_idp_NG021034_4</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -5555,7 +7544,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_3</t>
+          <t>non_idp_NG021034_5</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -5590,7 +7579,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rogogo</t>
+          <t>Garni</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5600,7 +7589,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_4</t>
+          <t>non_idp_NG021034_6</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -5635,7 +7624,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Garni</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5645,7 +7634,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_5</t>
+          <t>non_idp_NG021034_7</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -5690,7 +7679,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_6</t>
+          <t>non_idp_NG021034_8</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -5725,7 +7714,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Rogogo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5735,18 +7724,18 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_7</t>
+          <t>non_idp_NG021034_9</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5760,30 +7749,34 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Bungudu</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Garni</t>
+          <t>Bela Rawaiya</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_8</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
+          <t>idp_NG037005_1</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>6</t>
@@ -5805,38 +7798,42 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Zamfara</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Bungudu</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rogogo</t>
+          <t>Bungudu</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_9</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>idp_NG037005_16</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -5870,7 +7867,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>idp_NG037005_1</t>
+          <t>idp_NG037005_2</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5880,12 +7877,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -5909,7 +7906,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Kotorkoshi</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5919,7 +7916,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>idp_NG037005_16</t>
+          <t>idp_NG037005_6</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5929,12 +7926,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -5958,32 +7955,28 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bela Rawaiya</t>
+          <t>Furfuri Kwaikwai</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>idp_NG037005_2</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037005_1</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6007,32 +8000,28 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Samawa</t>
+          <t>Furfuri Kwaikwai</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>idp_NG037005_4</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037005_12</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6056,32 +8045,28 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kotorkoshi</t>
+          <t>Nahuche</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>idp_NG037005_6</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG037005_14</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6105,7 +8090,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Furfuri Kwaikwai</t>
+          <t>Bungudu</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6115,7 +8100,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_1</t>
+          <t>non_idp_NG037005_16</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -6150,7 +8135,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Gada Karakai</t>
+          <t>Furfuri Kwaikwai</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6160,7 +8145,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_10</t>
+          <t>non_idp_NG037005_17</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -6195,7 +8180,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Gada Karakai</t>
+          <t>Bela Rawaiya</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6205,7 +8190,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_11</t>
+          <t>non_idp_NG037005_2</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -6240,7 +8225,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Furfuri Kwaikwai</t>
+          <t>Bela Rawaiya</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6250,7 +8235,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_12</t>
+          <t>non_idp_NG037005_3</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -6285,7 +8270,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bingi South</t>
+          <t>Sankalawa</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6295,7 +8280,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_13</t>
+          <t>non_idp_NG037005_5</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -6330,7 +8315,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nahuche</t>
+          <t>Sankalawa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6340,7 +8325,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_14</t>
+          <t>non_idp_NG037005_6</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -6375,7 +8360,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bingi South</t>
+          <t>Kotorkoshi</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6385,7 +8370,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_15</t>
+          <t>non_idp_NG037005_8</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -6420,7 +8405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Bela Rawaiya</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6430,7 +8415,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_16</t>
+          <t>non_idp_NG037005_supp1</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -6465,7 +8450,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Furfuri Kwaikwai</t>
+          <t>Bingi North</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6475,7 +8460,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_17</t>
+          <t>non_idp_NG037005_supp2</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -6510,7 +8495,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bela Rawaiya</t>
+          <t>Nahuche</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6520,7 +8505,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_2</t>
+          <t>non_idp_NG037005_supp3</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -6555,7 +8540,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bela Rawaiya</t>
+          <t>Maru</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6565,7 +8550,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_3</t>
+          <t>non_idp_NG037005_supp4</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -6600,7 +8585,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Samawa</t>
+          <t>Kotorkoshi</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6610,7 +8595,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_4</t>
+          <t>non_idp_NG037005_supp5</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -6645,7 +8630,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sankalawa</t>
+          <t>Furfuri Kwaikwai</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6655,7 +8640,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_5</t>
+          <t>non_idp_NG037005_supp6</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -6690,7 +8675,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kotorkoshi</t>
+          <t>Furfuri Kwaikwai</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6700,7 +8685,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_6</t>
+          <t>non_idp_NG037005_supp7</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -6722,158 +8707,23 @@
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Bungudu</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Gada Karakai</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>non_idp_NG037005_7</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" s="10" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Bungudu</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Kotorkoshi</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>non_idp_NG037005_8</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" s="10" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Zamfara</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Bungudu</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Gada Karakai</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>non_idp_NG037005_9</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" s="10" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M79" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="M2:M76" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7139,13 +8989,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03697C5F-664B-4632-BFAF-E2E4433E3BAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{686BA147-40B3-40F1-B60F-0B1581A6243E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7D8A154-B6E6-43DE-BBAC-2F20CA090424}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB1571C0-9BB9-4A5A-8A4B-20E95DE8E48D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC82E544-9350-4C6F-AD52-64597F34F625}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09D53F38-E93D-4A4C-8C6E-A81015B8DE81}"/>
 </file>
--- a/resampling/input/accessibility_reports_generated/Save the Children_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/Save the Children_accessibility_report.xlsx
@@ -210,24 +210,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O76" headerRowCount="1">
-  <autoFilter ref="A1:O76"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:P82" headerRowCount="1">
+  <autoFilter ref="A1:P82"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
     <tableColumn id="3" name="Ward (GRID3)"/>
     <tableColumn id="4" name="Pop Type"/>
     <tableColumn id="5" name="Cluster ID"/>
-    <tableColumn id="6" name="IDP Category"/>
-    <tableColumn id="7" name="Target HHs (primary)"/>
-    <tableColumn id="8" name="Reserve HHs"/>
-    <tableColumn id="9" name="Accessible (Y/N)"/>
-    <tableColumn id="10" name="Reason category"/>
-    <tableColumn id="11" name="Reason notes"/>
-    <tableColumn id="12" name="% of target achieved so far"/>
-    <tableColumn id="13" name="Date reported"/>
-    <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
-    <tableColumn id="15" name="Source channel"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="IDP Category"/>
+    <tableColumn id="8" name="Target HHs (primary)"/>
+    <tableColumn id="9" name="Reserve HHs"/>
+    <tableColumn id="10" name="Accessible (Y/N)"/>
+    <tableColumn id="11" name="Reason category"/>
+    <tableColumn id="12" name="Reason notes"/>
+    <tableColumn id="13" name="% of target achieved so far"/>
+    <tableColumn id="14" name="Date reported"/>
+    <tableColumn id="15" name="Reported by (Partner / IMPACT-default)"/>
+    <tableColumn id="16" name="Source channel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -522,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -553,7 +554,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 95 wards, 75 clusters</t>
+          <t>Assigned to you: 95 wards, 81 clusters</t>
         </is>
       </c>
     </row>
@@ -580,7 +581,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
+          <t>If you've reported on a row before, your last answer is already shown here (Accessible/Reason/Date reported etc.) rather than a blank cell - please review it and only change it if something has actually changed since you last told us, don't assume a filled-in row is a mistake. On the 'Cluster Accessibility' sheet, a cluster you previously flagged that's since been removed from your assigned list entirely still appears, marked 'No longer in frame' in the Status column - kept so your earlier report isn't lost, but it's no longer something we need action on.</t>
         </is>
       </c>
     </row>
@@ -590,7 +591,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
+          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
         </is>
       </c>
     </row>
@@ -600,7 +601,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
+          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
         </is>
       </c>
     </row>
@@ -610,7 +611,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
+          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
         </is>
       </c>
     </row>
@@ -620,7 +621,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
+          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
         </is>
       </c>
     </row>
@@ -630,7 +631,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
         </is>
       </c>
     </row>
@@ -640,58 +641,68 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>IMPORTANT: please review your ENTIRE coverage area in one pass before sending this back to us, rather than reporting a few wards now and more later - this significantly cuts down the back-and-forth rounds we need with you. If genuinely new information comes in afterwards, send an updated copy of the FULL sheet (not just the changed rows) with a new Date reported - we track changes over time by date, so we don't need you to tell us what changed, just the current full picture.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Use for</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Ward Accessibility</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>Ward Accessibility</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -833,7 +844,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Liev L</t>
+          <t>Mbaikyor</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -845,13 +856,13 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -874,7 +885,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Liev Ll</t>
+          <t>Yaav</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -886,13 +897,13 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -915,7 +926,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mbaikyor</t>
+          <t>Mbadura</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -927,13 +938,13 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -956,7 +967,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Menev</t>
+          <t>Liev L</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -968,13 +979,13 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -997,7 +1008,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tondov Ll</t>
+          <t>Liev Ll</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1009,13 +1020,13 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1038,7 +1049,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yaav</t>
+          <t>Menev</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1050,10 +1061,10 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>8</v>
@@ -1079,7 +1090,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mbadura</t>
+          <t>Tondov Ll</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1091,13 +1102,13 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1914,10 +1925,10 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -1940,7 +1951,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ubandawaki A</t>
+          <t>Natsalle</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1951,7 +1962,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Daura</t>
+          <t>Mashi</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1960,13 +1971,13 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2009,13 +2020,13 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2058,13 +2069,13 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2087,25 +2098,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Natsalle</t>
+          <t>Maikoni B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Mashi</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>5</v>
       </c>
@@ -2113,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2136,25 +2139,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gallu</t>
+          <t>Bumbum B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Mashi</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -2162,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2185,7 +2180,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Maikoni B</t>
+          <t>Koza</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2197,13 +2192,13 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2226,7 +2221,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bumbum B</t>
+          <t>Bumbum A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -2238,13 +2233,13 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2267,17 +2262,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Koza</t>
+          <t>Gallu</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mashi</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H36" t="n">
         <v>1</v>
       </c>
@@ -2285,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2308,7 +2311,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sabon Gari</t>
+          <t>Ubandawaki B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -2319,7 +2322,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bindawa; Charanchi; Daura; Funtua; Mani; Rimi; Sandamu</t>
+          <t>Daura</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2334,7 +2337,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2377,13 +2380,13 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -2406,25 +2409,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bumbum A</t>
+          <t>Karkarku</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Daura; Sandamu</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -2447,7 +2458,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ubandawaki B</t>
+          <t>Kusugu</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2467,13 +2478,13 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2496,7 +2507,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Karkarku</t>
+          <t>Kwasarawa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2507,7 +2518,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Daura; Sandamu</t>
+          <t>Sandamu; Zango</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2545,25 +2556,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kusugu</t>
+          <t>Mai'adua B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Daura</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>0</v>
       </c>
@@ -2594,25 +2597,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kwasarawa</t>
+          <t>Mai'adua C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Sandamu; Zango</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>0</v>
       </c>
@@ -2643,17 +2638,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mai'adua B</t>
+          <t>Mazoji A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Daura; Matazu</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
@@ -2684,17 +2687,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mai'adua C</t>
+          <t>Mazoji B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Daura; Matazu</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
@@ -2725,7 +2736,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mazoji A</t>
+          <t>Sabon Gari</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2736,7 +2747,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Daura; Matazu</t>
+          <t>Bindawa; Charanchi; Daura; Funtua; Mani; Rimi; Sandamu</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2774,7 +2785,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mazoji B</t>
+          <t>Sirika B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -2785,7 +2796,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Daura; Matazu</t>
+          <t>Daura; Dutsi; Mani</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2823,7 +2834,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sirika B</t>
+          <t>Sonkaya</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -2834,7 +2845,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Daura; Dutsi; Mani</t>
+          <t>Dutsi; Mashi</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2872,7 +2883,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sonkaya</t>
+          <t>Ubandawaki A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -2883,7 +2894,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dutsi; Mashi</t>
+          <t>Daura</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2947,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -3011,19 +3022,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Dargage</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -3052,25 +3071,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>K Malamai</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Baure</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>2</v>
       </c>
@@ -3078,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3101,7 +3112,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dargage</t>
+          <t>K Malamai</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -3112,7 +3123,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sandamu</t>
+          <t>Baure</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3127,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3191,25 +3202,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kawarin Kudi</t>
+          <t>Gwamba</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Baure</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>1</v>
       </c>
@@ -3217,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -3240,7 +3243,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fago B</t>
+          <t>Baure</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -3251,7 +3254,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sandamu</t>
+          <t>Baure; Bindawa; Mani</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3260,13 +3263,13 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -3289,25 +3292,33 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gwamba</t>
+          <t>Fago B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Sandamu</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -3330,7 +3341,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Baure</t>
+          <t>Faski</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -3341,7 +3352,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Baure; Bindawa; Mani</t>
+          <t>Baure</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3379,7 +3390,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faski</t>
+          <t>Gwarta</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -3428,7 +3439,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gwarta</t>
+          <t>Kagare</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -3439,7 +3450,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Baure</t>
+          <t>Sandamu</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3477,7 +3488,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kagare</t>
+          <t>Katsayal</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -3526,7 +3537,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Katsayal</t>
+          <t>Kawarin Kudi</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -3537,7 +3548,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sandamu</t>
+          <t>Baure</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3644,7 +3655,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -3881,13 +3892,13 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
       </c>
       <c r="J70" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
@@ -4098,7 +4109,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Bindin</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -4109,7 +4120,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Maradun; Maru</t>
+          <t>Anka; Maru</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4118,13 +4129,13 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
@@ -4147,7 +4158,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bindin</t>
+          <t>Bingi</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -4158,7 +4169,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Anka; Maru</t>
+          <t>Maru</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4196,7 +4207,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bingi</t>
+          <t>Bingi South</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -4207,7 +4218,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Gusau; Maru</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4245,7 +4256,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bingi South</t>
+          <t>Damaga Gamagiwa</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -4256,7 +4267,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gusau; Maru</t>
+          <t>Maradun; Maru</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4294,7 +4305,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Damaga Gamagiwa</t>
+          <t>Dan' Isa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -4305,7 +4316,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Maradun; Maru</t>
+          <t>Birnin Magaji; Kaura Namoda</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4343,7 +4354,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dan' Isa</t>
+          <t>Gada Karakai</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -4354,7 +4365,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Birnin Magaji; Kaura Namoda</t>
+          <t>Maradun; Maru</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4392,7 +4403,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Gada Karakai</t>
+          <t>Galadima</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -4403,7 +4414,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Maradun; Maru</t>
+          <t>Anka; Bakura; Gusau; Talata Mafara</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4441,7 +4452,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Galadima</t>
+          <t>Kagara</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -4452,7 +4463,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Anka; Bakura; Gusau; Talata Mafara</t>
+          <t>Birnin Magaji; Kaura Namoda; Talata Mafara</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4490,7 +4501,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kagara</t>
+          <t>Kanoma</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -4501,7 +4512,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Birnin Magaji; Kaura Namoda; Talata Mafara</t>
+          <t>Anka; Maru; Talata Mafara</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4539,7 +4550,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kanoma</t>
+          <t>Kurya</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -4550,7 +4561,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Anka; Maru; Talata Mafara</t>
+          <t>Kaura Namoda; Maradun; Shinkafi; Zurmi</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4588,7 +4599,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kurya</t>
+          <t>Kyambarawa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -4599,7 +4610,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kaura Namoda; Maradun; Shinkafi; Zurmi</t>
+          <t>Birnin Magaji; Kaura Namoda</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4637,7 +4648,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kyambarawa</t>
+          <t>Magami</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -4648,7 +4659,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Birnin Magaji; Kaura Namoda</t>
+          <t>Gusau; Maru; Tsafe</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4686,7 +4697,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Magami</t>
+          <t>Maru</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -4697,7 +4708,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gusau; Maru; Tsafe</t>
+          <t>Maradun; Maru</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5171,7 +5182,7 @@
     </dataValidation>
     <dataValidation sqref="O2:O96" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5187,7 +5198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:P82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5195,16 +5206,17 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5235,50 +5247,55 @@
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
           <t>IDP Category</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Target HHs (primary)</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Reserve HHs</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Accessible (Y/N)</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Reason category</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Reason notes</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>% of target achieved so far</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Date reported</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Reported by (Partner / IMPACT-default)</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Source channel</t>
         </is>
@@ -5312,26 +5329,55 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Few IDPs available</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5361,26 +5407,55 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5410,26 +5485,55 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Not completed</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5459,26 +5563,55 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5508,26 +5641,55 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5557,26 +5719,31 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5596,18 +5763,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_10</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>idp_NG007011_supp3</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -5615,13 +5786,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5636,23 +5812,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Menev</t>
+          <t>Mbaikyor</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_11</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>idp_NG007011_supp4</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -5660,13 +5840,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5681,23 +5866,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Menev</t>
+          <t>Yaav</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_12</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>idp_NG007011_supp5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -5705,13 +5894,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5726,23 +5920,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Liev Ll</t>
+          <t>Yaav</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_13</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>idp_NG007011_supp6</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5750,13 +5948,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5771,23 +5974,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mbaketsa</t>
+          <t>Mbadura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_14</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>idp_NG007011_supp7</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5795,13 +6002,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5816,23 +6028,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yaav</t>
+          <t>Mbadura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_16</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>idp_NG007011_supp8</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5840,13 +6056,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5871,27 +6092,56 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_17</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_10</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Coordinates fall witin farmlands, over 500m to the nearest HH</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5906,7 +6156,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mbaketsa</t>
+          <t>Menev</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5916,27 +6166,56 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_2</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_11</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Not completed</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5951,7 +6230,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Usar</t>
+          <t>Menev</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5961,27 +6240,56 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_3</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_12</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Points not located</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5996,7 +6304,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mbaikyor</t>
+          <t>Liev Ll</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -6006,27 +6314,56 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_4</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_13</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6041,7 +6378,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tondov Ll</t>
+          <t>Mbaketsa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6051,27 +6388,56 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_5</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_14</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6086,7 +6452,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Agba / Kyan</t>
+          <t>Yaav</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6096,27 +6462,56 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_7</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_16</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Not completed</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6131,7 +6526,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tondov Ll</t>
+          <t>Mbaikyor</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6141,27 +6536,56 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_8</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_17</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6176,7 +6600,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Agba / Kyan</t>
+          <t>Mbaketsa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6186,27 +6610,56 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_9</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_2</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6221,7 +6674,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Liev L</t>
+          <t>Usar</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6231,27 +6684,56 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_supp1</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6266,7 +6748,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Liev Ll</t>
+          <t>Mbaikyor</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6276,140 +6758,219 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>non_idp_NG007011_supp2</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_4</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Coordinates fall witin farmlands, over 500m to the nearest HH</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mai'adua A</t>
+          <t>Tondov Ll</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>idp_NG021024_1</t>
+          <t>non_idp_NG007011_5</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Not completed</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ubandawaki A</t>
+          <t>Agba / Kyan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>idp_NG021024_10</t>
+          <t>non_idp_NG007011_7</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gallu</t>
+          <t>Tondov Ll</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6419,42 +6980,71 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_8</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non compliance by some community members even after obtaining access through the community leader. </t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Danyashe</t>
+          <t>Agba / Kyan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -6464,42 +7054,71 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_10</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_9</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Some points not found</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Natsalle</t>
+          <t>Liev L</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6509,42 +7128,47 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_11</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_supp1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Katsina</t>
+          <t>Benue</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mai'adua</t>
+          <t>Kwande</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Maikoni B</t>
+          <t>Liev Ll</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6554,27 +7178,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_12</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG007011_supp2</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6589,37 +7218,46 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Maikoni A</t>
+          <t>Mai'adua A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_13</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>idp_NG021024_1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6634,37 +7272,46 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ubandawaki A</t>
+          <t>Natsalle</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_15</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>idp_NG021024_supp1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6679,23 +7326,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bumbum B</t>
+          <t>Natsalle</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_17</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>idp_NG021024_supp2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6703,13 +7354,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6729,18 +7385,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_2</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>idp_NG021024_supp3</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6748,13 +7408,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6769,23 +7434,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Natsalle</t>
+          <t>Mai'adua A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_3</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>idp_NG021024_supp4</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -6793,13 +7462,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6824,27 +7498,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_4</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_10</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6869,27 +7548,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_5</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_11</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6904,7 +7588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Danyashe</t>
+          <t>Maikoni B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6914,27 +7598,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_6</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_12</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6949,7 +7638,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Natsalle</t>
+          <t>Maikoni A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6959,27 +7648,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_7</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_13</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6994,7 +7688,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Maikoni A</t>
+          <t>Bumbum B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -7004,27 +7698,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_8</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_17</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7039,7 +7738,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Maikoni A</t>
+          <t>Natsalle</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -7049,27 +7748,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG021024_9</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_2</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="10" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7079,12 +7783,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dargage</t>
+          <t>Natsalle</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -7094,27 +7798,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_1</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_3</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7124,12 +7833,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>K Malamai</t>
+          <t>Danyashe</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7139,27 +7848,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_11</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_4</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="10" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7169,12 +7883,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kanda</t>
+          <t>Natsalle</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7184,27 +7898,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_12</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_5</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7214,12 +7933,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gwamba</t>
+          <t>Danyashe</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7229,27 +7948,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_13</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_6</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="10" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7259,12 +7983,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>K Malamai</t>
+          <t>Natsalle</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7274,27 +7998,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_15</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_7</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7304,12 +8033,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kawarin Kudi</t>
+          <t>Maikoni A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7319,27 +8048,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_16</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_8</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="10" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7349,12 +8083,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Garni</t>
+          <t>Maikoni A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7364,27 +8098,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_17</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_9</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="10" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7394,12 +8133,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Maikoni A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7409,27 +8148,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_2</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_supp1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="10" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7439,12 +8183,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Zango</t>
+          <t>Mai'adua</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Garni</t>
+          <t>Danyashe</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7454,27 +8198,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_3</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021024_supp2</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" s="10" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7489,7 +8238,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rogogo</t>
+          <t>Dargage</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7499,27 +8248,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_4</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021034_1</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" s="10" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7534,7 +8288,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Garni</t>
+          <t>K Malamai</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7544,27 +8298,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_5</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021034_11</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" s="10" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7579,7 +8338,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Garni</t>
+          <t>Kanda</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7589,27 +8348,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_6</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021034_12</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" s="10" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7624,7 +8388,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Gwamba</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7634,27 +8398,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_7</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021034_13</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7669,7 +8438,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Garni</t>
+          <t>K Malamai</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7679,27 +8448,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_8</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021034_15</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" s="10" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7714,7 +8488,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rogogo</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7724,238 +8498,247 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>non_idp_NG021034_9</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>non_idp_NG021034_2</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bela Rawaiya</t>
+          <t>Garni</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>idp_NG037005_1</t>
+          <t>non_idp_NG021034_3</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" s="10" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Rogogo</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>idp_NG037005_16</t>
+          <t>non_idp_NG021034_4</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bela Rawaiya</t>
+          <t>Garni</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>idp_NG037005_2</t>
+          <t>non_idp_NG021034_6</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" s="10" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kotorkoshi</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>idp_NG037005_6</t>
+          <t>non_idp_NG021034_7</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" s="10" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Furfuri Kwaikwai</t>
+          <t>Garni</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7965,42 +8748,47 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_1</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021034_8</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" s="10" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Furfuri Kwaikwai</t>
+          <t>Rogogo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8010,42 +8798,47 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_12</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021034_9</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" s="10" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nahuche</t>
+          <t>Garni</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8055,42 +8848,47 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_14</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021034_supp1</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" s="10" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Zamfara</t>
+          <t>Katsina</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Zango</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bungudu</t>
+          <t>Dargage</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8100,27 +8898,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_16</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG021034_supp2</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" s="10" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8135,23 +8938,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Furfuri Kwaikwai</t>
+          <t>Bela Rawaiya</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_17</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>idp_NG037005_1</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -8159,13 +8966,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" s="10" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8180,23 +8992,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bela Rawaiya</t>
+          <t>Bungudu</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_2</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>idp_NG037005_16</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -8204,13 +9020,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" s="10" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8230,32 +9051,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_3</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>idp_NG037005_2</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" s="10" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8270,37 +9100,46 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sankalawa</t>
+          <t>Kotorkoshi</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_5</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>idp_NG037005_6</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" s="10" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8315,7 +9154,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sankalawa</t>
+          <t>Furfuri Kwaikwai</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8325,27 +9164,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_6</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037005_1</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" s="10" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8360,7 +9204,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kotorkoshi</t>
+          <t>Furfuri Kwaikwai</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8370,27 +9214,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_8</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037005_12</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" s="10" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8405,7 +9254,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bela Rawaiya</t>
+          <t>Nahuche</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8415,27 +9264,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_supp1</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037005_14</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" s="10" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8450,7 +9304,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bingi North</t>
+          <t>Bungudu</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8460,27 +9314,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_supp2</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037005_16</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" s="10" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8495,7 +9354,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nahuche</t>
+          <t>Furfuri Kwaikwai</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8505,27 +9364,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_supp3</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037005_17</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" s="10" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8540,7 +9404,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Maru</t>
+          <t>Bela Rawaiya</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8550,27 +9414,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_supp4</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037005_2</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" s="10" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8585,7 +9454,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kotorkoshi</t>
+          <t>Bela Rawaiya</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8595,27 +9464,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_supp5</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037005_3</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" s="10" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8630,7 +9504,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Furfuri Kwaikwai</t>
+          <t>Sankalawa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8640,27 +9514,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_supp6</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037005_5</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" s="10" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8675,7 +9554,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Furfuri Kwaikwai</t>
+          <t>Sankalawa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -8685,45 +9564,350 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>non_idp_NG037005_supp7</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG037005_6</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" s="10" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Bela Rawaiya</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>non_idp_NG037005_supp1</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Bingi North</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>non_idp_NG037005_supp2</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Nahuche</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>non_idp_NG037005_supp3</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Kotorkoshi</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>non_idp_NG037005_supp5</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Furfuri Kwaikwai</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>non_idp_NG037005_supp6</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Bungudu</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Furfuri Kwaikwai</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>non_idp_NG037005_supp7</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M76" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="N2:N82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8989,13 +10173,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{686BA147-40B3-40F1-B60F-0B1581A6243E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1A4F21F-FC9B-461D-A1B7-618A95FDD300}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB1571C0-9BB9-4A5A-8A4B-20E95DE8E48D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E9D6AE8-3990-452B-B0B0-A991DE9709B7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09D53F38-E93D-4A4C-8C6E-A81015B8DE81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7D45800-717E-4EDA-AC0B-1F4F03916278}"/>
 </file>